--- a/src/test/resources/TestDataFolder/DemoWebShopExcelSheet.xlsx
+++ b/src/test/resources/TestDataFolder/DemoWebShopExcelSheet.xlsx
@@ -9,12 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="LogInSheet" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="NewCreatedSheet" r:id="rId6" sheetId="3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -670,22 +669,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/src/test/resources/TestDataFolder/DemoWebShopExcelSheet.xlsx
+++ b/src/test/resources/TestDataFolder/DemoWebShopExcelSheet.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\NewSeleniumWorkspace\DemoWebShopFramework_A16\src\test\resources\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="LogInSheet" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="24">
   <si>
     <t>UserName</t>
   </si>
@@ -93,23 +93,16 @@
     <t>themail10@gmail.com</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
     <t>themail11@gmail.com</t>
   </si>
   <si>
     <t>Password@4321</t>
-  </si>
-  <si>
-    <t>Email</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -432,25 +425,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="19.140625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="15.42578125"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s" s="0">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -458,7 +448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -466,7 +456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -474,7 +464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -482,7 +472,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -490,7 +480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -498,7 +488,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -506,7 +496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -514,7 +504,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
@@ -522,7 +512,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -530,12 +520,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s" s="0">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
         <v>23</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -561,15 +551,15 @@
   <dimension ref="E4:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="21.140625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="15.42578125"/>
+    <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E4" t="s" s="0">
+      <c r="E4" t="s">
         <v>0</v>
       </c>
-      <c r="F4" t="s" s="0">
+      <c r="F4" t="s">
         <v>1</v>
       </c>
     </row>

--- a/src/test/resources/TestDataFolder/DemoWebShopExcelSheet.xlsx
+++ b/src/test/resources/TestDataFolder/DemoWebShopExcelSheet.xlsx
@@ -9,11 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="LogInSheet" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="RegisterSheet" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>UserName</t>
   </si>
@@ -97,13 +97,37 @@
   </si>
   <si>
     <t>Password@4321</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>ConfirmPassword</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Doe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,16 +143,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -136,14 +174,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -548,115 +602,62 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="E4:F14"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E5" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>12</v>
+      <c r="F2" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1"/>
-    <hyperlink ref="E5" r:id="rId2"/>
-    <hyperlink ref="E6" r:id="rId3"/>
-    <hyperlink ref="E7" r:id="rId4"/>
-    <hyperlink ref="E8" r:id="rId5"/>
-    <hyperlink ref="E9" r:id="rId6"/>
-    <hyperlink ref="E10" r:id="rId7"/>
-    <hyperlink ref="E11" r:id="rId8"/>
-    <hyperlink ref="E12" r:id="rId9"/>
-    <hyperlink ref="E13" r:id="rId10"/>
-    <hyperlink ref="E14" r:id="rId11"/>
+    <hyperlink ref="D2" r:id="rId1"/>
+    <hyperlink ref="E2" r:id="rId2"/>
+    <hyperlink ref="F2" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>